--- a/data/아실_매교역팰루시드_전체매물_20261014.xlsx
+++ b/data/아실_매교역팰루시드_전체매물_20261014.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA42"/>
+  <dimension ref="A1:AA39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,12 +564,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>43160256</t>
+          <t>43166549</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -579,27 +579,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>122동</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>101.34</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>71.89</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -620,17 +620,17 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -639,18 +639,18 @@
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>O</t>
@@ -658,17 +658,17 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>O전입O대출X채광좋은층O당일확인,중문,현관고급화</t>
+          <t>O대출가능,전입가능O2면창채광좋은집,에어컨4대</t>
         </is>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="AA2" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -684,7 +684,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43160257</t>
+          <t>43166533</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -694,27 +694,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>120동</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>101.02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -757,19 +757,11 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>O채광좋은층O당일확인,중문,현관고급화</t>
+          <t>O가격협의가능O이강에서집봐요,조건맞춰드립니다</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -795,7 +787,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>43126870</t>
+          <t>43165287</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,27 +797,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>111동</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>129.28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>101.73</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -841,7 +833,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>116,830</t>
+          <t>119,720</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -856,7 +848,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -865,13 +857,13 @@
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
@@ -880,11 +872,11 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>O이강은조건맞춰드립니다O뻥뷰,중도금대출승계가능</t>
+          <t>O정원뷰O2층커뮤니티동귀한대형평형시스템에어컨6대무상</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>116830</v>
+        <v>119720</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -901,12 +893,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>43125582</t>
+          <t>43165270</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -916,27 +908,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>125동</t>
+          <t>102동</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -947,17 +939,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115,030</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -967,7 +959,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -976,17 +968,9 @@
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
@@ -995,14 +979,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>O4년거주가능O대출가능,뻥뷰,에어컨4,인덕션등</t>
+          <t>OP2.3억O당일확인,귀한트인조망,채광환기굿</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>115030</v>
       </c>
       <c r="Z5" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1016,12 +1000,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>43125573</t>
+          <t>43165233</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1031,27 +1015,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>122동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>101.34</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>71.89</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>고</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1062,17 +1046,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>116,830</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1082,7 +1066,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1091,11 +1075,7 @@
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
@@ -1110,14 +1090,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>O대출가능,전입가능O2면창채광좋은집,에어컨4대</t>
+          <t>O이강은조건맞춰드립니다O뻥뷰,중도금대출승계가능</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>116830</v>
       </c>
       <c r="Z6" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1136,7 +1116,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>43125226</t>
+          <t>43199433</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1146,17 +1126,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>126동</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.42</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1166,7 +1146,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1187,7 +1167,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1197,7 +1177,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1211,28 +1191,28 @@
           <t>O</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O채광좋은남동향,시에4,입주협의</t>
+          <t>O대출가능O융자없음.가전원옵션풀,시스템에어컨풀</t>
         </is>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1246,12 +1226,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>43124673</t>
+          <t>43164394</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1261,27 +1241,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>111동</t>
+          <t>109동</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>129.28</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>101.73</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1292,17 +1272,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115,272</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>70,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1312,7 +1292,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1321,29 +1301,29 @@
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>O전세는이강O귀한101타입,채광굿,입주일협의가능</t>
+          <t>O정상거래는이강O당일확인,에어컨4,붙박이장,인덕션</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>115272</v>
       </c>
       <c r="Z8" t="n">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1362,7 +1342,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>43124662</t>
+          <t>43164195</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1372,7 +1352,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>111동</t>
+          <t>117동</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1392,7 +1372,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1423,7 +1403,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1432,26 +1412,22 @@
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
-          <t>O전세대출가능O융자없음,인덕션,시스템에어컨4,입주협의</t>
+          <t>O매물답사가능O전세대출가능,냉장고,냉동,김냉,인덕션등</t>
         </is>
       </c>
       <c r="Y9" t="n">
@@ -1477,7 +1453,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>43070764</t>
+          <t>43164078</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1487,7 +1463,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>119동</t>
+          <t>103동</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1507,7 +1483,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1528,7 +1504,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1538,7 +1514,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1547,25 +1523,25 @@
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>O애완동물O,가격협의가O와이드주방,채광좋아요,조용하고따뜻한동</t>
+          <t>O조건맞춰드립니다O초등학교인접인기동,시스템에어컨풀</t>
         </is>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>55000</v>
+        <v>50000</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1584,7 +1560,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>43070729</t>
+          <t>43160256</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1594,12 +1570,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>126동</t>
+          <t>104동</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>84.42</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1614,7 +1590,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1635,17 +1611,17 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1654,32 +1630,36 @@
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>O초역세권동,전입가능O에어컨4,붙박이장,냉장고3,인덕션등</t>
+          <t>O전입O대출X채광좋은층O당일확인,중문,현관고급화</t>
         </is>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="AA11" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12">
@@ -1690,12 +1670,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>43070716</t>
+          <t>43160257</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1705,27 +1685,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>107동</t>
+          <t>104동</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1736,7 +1716,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1746,17 +1726,17 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1766,13 +1746,13 @@
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr">
         <is>
           <t>O</t>
@@ -1780,17 +1760,17 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>O전입가능O입주협의,융무,채광좋은집</t>
+          <t>O채광좋은층O당일확인,중문,현관고급화</t>
         </is>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>10000</v>
+        <v>45000</v>
       </c>
       <c r="AA12" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1801,12 +1781,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>43070705</t>
+          <t>43125226</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1816,27 +1796,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>102동</t>
+          <t>104동</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1847,17 +1827,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>115,030</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1867,7 +1847,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1876,8 +1856,16 @@
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
@@ -1887,14 +1875,14 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>OP2.3억O당일확인,귀한트인조망,채광환기굿</t>
+          <t>O조건맞춰드립니다O채광좋은남동향,시에4,입주협의</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>115030</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -1908,12 +1896,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>43070693</t>
+          <t>43124673</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1923,7 +1911,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>110동</t>
+          <t>111동</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1943,7 +1931,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -1954,17 +1942,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>119,372</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70,000</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1974,7 +1962,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1984,13 +1972,13 @@
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>O</t>
@@ -1998,14 +1986,14 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>O피500O로얄동,에어컨6,붙박이장,따뜻한단지조경뷰</t>
+          <t>O전세는이강O귀한101타입,채광굿,입주일협의가능</t>
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>119372</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2019,12 +2007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>43070686</t>
+          <t>43124662</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2039,22 +2027,22 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>129.28</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>101.73</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2065,17 +2053,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>119,720</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2085,7 +2073,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2099,24 +2087,28 @@
           <t>O</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
-          <t>O정원뷰O2층커뮤니티동귀한대형평형시스템에어컨6대무상</t>
+          <t>O전세대출가능O융자없음,인덕션,시스템에어컨4,입주협의</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>119720</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2135,7 +2127,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>43028211</t>
+          <t>43070764</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2145,7 +2137,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>119동</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2165,7 +2157,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2186,7 +2178,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>53,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2196,7 +2188,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2206,11 +2198,7 @@
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
@@ -2220,14 +2208,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>O채광좋은층O현금전세,밝고환한집,입주일협의</t>
+          <t>O애완동물O,가격협의가O와이드주방,채광좋아요,조용하고따뜻한동</t>
         </is>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>53000</v>
+        <v>55000</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2241,12 +2229,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>43060055</t>
+          <t>43070729</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2256,27 +2244,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>119동</t>
+          <t>126동</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>84.42</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -2287,7 +2275,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2297,17 +2285,17 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>53,000</t>
+          <t>15,000</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>160</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2316,28 +2304,32 @@
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O현금전세,따뜻한단지내뷰,융무</t>
+          <t>O초역세권동,전입가능O에어컨4,붙박이장,냉장고3,인덕션등</t>
         </is>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>53000</v>
+        <v>15000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18">
@@ -2348,12 +2340,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>43026195</t>
+          <t>43070716</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2363,27 +2355,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>120동</t>
+          <t>107동</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>101.02</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2394,7 +2386,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2404,17 +2396,17 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2424,23 +2416,31 @@
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>O가격협의가능O이강에서집봐요,조건맞춰드립니다</t>
+          <t>O전입가능O입주협의,융무,채광좋은집</t>
         </is>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>45000</v>
+        <v>10000</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>43026187</t>
+          <t>43070693</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2466,27 +2466,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>131동</t>
+          <t>110동</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>74.16</t>
+          <t>129.28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>101.73</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2497,17 +2497,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>119,372</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2526,11 +2526,7 @@
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
@@ -2538,17 +2534,21 @@
           <t>O</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>O이.강O시에3,냉장고,냉동고,김치냉장고,워시타워,인덕션</t>
+          <t>O피500O로얄동,에어컨6,붙박이장,따뜻한단지조경뷰</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>119372</v>
       </c>
       <c r="Z19" t="n">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>43060057</t>
+          <t>43060055</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2577,27 +2577,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>126동</t>
+          <t>119동</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>84.42</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>53,000</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2637,33 +2637,25 @@
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>O대출가능O융자없음.가전원옵션풀,시스템에어컨풀</t>
+          <t>O조건맞춰드립니다O현금전세,따뜻한단지내뷰,융무</t>
         </is>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>50000</v>
+        <v>53000</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -2677,12 +2669,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>42954753</t>
+          <t>43026187</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2692,27 +2684,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>129동</t>
+          <t>131동</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>84.42</t>
+          <t>74.16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -2723,17 +2715,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>89,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2743,7 +2735,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2752,7 +2744,11 @@
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
@@ -2763,14 +2759,14 @@
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
-          <t>O조합원O필요금액확인요망,중문,초역세권동</t>
+          <t>O이.강O시에3,냉장고,냉동고,김치냉장고,워시타워,인덕션</t>
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>89000</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -2784,12 +2780,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>42952893</t>
+          <t>42954753</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2799,27 +2795,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>103동</t>
+          <t>129동</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>84.42</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -2830,17 +2826,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>89,000</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2859,25 +2855,25 @@
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O초등학교인접인기동,시스템에어컨풀</t>
+          <t>O조합원O필요금액확인요망,중문,초역세권동</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>89000</v>
       </c>
       <c r="Z22" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3550,7 +3546,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>42952544</t>
+          <t>42952449</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3560,7 +3556,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>109동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3580,7 +3576,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -3596,7 +3592,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>115,272</t>
+          <t>114,530</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3635,11 +3631,11 @@
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr">
         <is>
-          <t>O정상거래는이강O당일확인,에어컨4,붙박이장,인덕션</t>
+          <t>O피2.5억O셔세권동,필로티2층,시에4.중문</t>
         </is>
       </c>
       <c r="Y29" t="n">
-        <v>115272</v>
+        <v>114530</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3656,12 +3652,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>42952449</t>
+          <t>42952439</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3691,7 +3687,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -3702,17 +3698,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>114,530</t>
+          <t>116,830</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52,000</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3738,22 +3734,22 @@
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>O피2.5억O셔세권동,필로티2층,시에4.중문</t>
+          <t>O뻥뷰O현금전세,거실넓어요,에어컨4</t>
         </is>
       </c>
       <c r="Y30" t="n">
-        <v>114530</v>
+        <v>116830</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>52000</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -3772,7 +3768,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>42952439</t>
+          <t>42962670</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3782,7 +3778,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>105동</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3802,7 +3798,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -3818,12 +3814,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>116,830</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>52,000</t>
+          <t>53,000</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3842,11 +3838,7 @@
         </is>
       </c>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
@@ -3857,14 +3849,14 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>O뻥뷰O현금전세,거실넓어요,에어컨4</t>
+          <t>O현금전세O이.강조용한단지내뷰,나무보여요</t>
         </is>
       </c>
       <c r="Y31" t="n">
-        <v>116830</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>52000</v>
+        <v>53000</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -3883,7 +3875,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>42962670</t>
+          <t>42918213</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3893,7 +3885,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>105동</t>
+          <t>102동</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3913,7 +3905,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -3934,7 +3926,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>53,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3944,7 +3936,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3955,23 +3947,23 @@
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
         <is>
-          <t>O현금전세O이.강조용한단지내뷰,나무보여요</t>
+          <t>O조건맞춰드립니다O대출X초등학교가까운인기동</t>
         </is>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>53000</v>
+        <v>55000</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -3990,7 +3982,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>42918213</t>
+          <t>42852176</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4000,7 +3992,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>102동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4020,7 +4012,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>고</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -4041,7 +4033,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -4051,7 +4043,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -4067,18 +4059,22 @@
           <t>O</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O대출X초등학교가까운인기동</t>
+          <t>O조건맞춰드립니다O전세대출가능,조합원옵션굿</t>
         </is>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>55000</v>
+        <v>60000</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4097,7 +4093,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>42852176</t>
+          <t>42747074</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4107,27 +4103,27 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>129동</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>고</t>
+          <t>저</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -4148,7 +4144,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>47,000</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -4158,7 +4154,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -4168,7 +4164,11 @@
       </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>O</t>
@@ -4182,14 +4182,14 @@
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O전세대출가능,조합원옵션굿</t>
+          <t>O전세대출가능O매교역가까운동.빠른입주,중문인테리어</t>
         </is>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>60000</v>
+        <v>47000</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>42747074</t>
+          <t>42704440</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4218,33 +4218,33 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>129동</t>
+          <t>114동</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>저</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>47,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -4278,12 +4278,12 @@
         </is>
       </c>
       <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
           <t>O</t>
@@ -4293,14 +4293,14 @@
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
         <is>
-          <t>O전세대출가능O입주일협의,깨끗하게입주가능해요</t>
+          <t>O조건맞춰드립니다O전세대출가능,반전세가능,시스템풀</t>
         </is>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>47000</v>
+        <v>60000</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>42704440</t>
+          <t>42558979</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4329,33 +4329,33 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>114동</t>
+          <t>128동</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>101.02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -4389,29 +4389,29 @@
         </is>
       </c>
       <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O전세대출가능,반전세가능,시스템풀</t>
+          <t>O71타입로얄동O채광굿,입주협의가능</t>
         </is>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>60000</v>
+        <v>55000</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>42558979</t>
+          <t>42490328</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4440,33 +4440,33 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>128동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>101.02</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -4500,29 +4500,33 @@
         </is>
       </c>
       <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T37" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr">
         <is>
-          <t>O71타입로얄동O채광굿,입주협의가능</t>
+          <t>O늦은입주OKO시에4,실링팬,중문,입주청소,예쁜집</t>
         </is>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>55000</v>
+        <v>60000</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -4541,7 +4545,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>42490328</t>
+          <t>42490321</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4551,7 +4555,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>109동</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4571,7 +4575,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>고</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -4592,7 +4596,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>57,000</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4611,17 +4615,17 @@
         </is>
       </c>
       <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V38" t="inlineStr">
         <is>
           <t>O</t>
@@ -4630,14 +4634,14 @@
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr">
         <is>
-          <t>O늦은입주OKO시에4,실링팬,중문,입주청소,예쁜집</t>
+          <t>O전세대출가능O입주청소,줄눈,탄성코팅,냉장고3대,인덕션등</t>
         </is>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>60000</v>
+        <v>57000</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -4656,7 +4660,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>42490321</t>
+          <t>42441234</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4666,7 +4670,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>109동</t>
+          <t>110동</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4686,7 +4690,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>고</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -4707,7 +4711,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>57,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4717,7 +4721,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -4732,350 +4736,21 @@
           <t>O</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr">
         <is>
-          <t>O전세대출가능O입주청소,줄눈,탄성코팅,냉장고3대,인덕션등</t>
+          <t>O조건맞춰드립니다O커뮤니티코앞,동간격넓은동,입주일협의가능</t>
         </is>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>57000</v>
+        <v>60000</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>전세</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>42490045</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>매교역팰루시드</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>117동</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>112.60</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>84.14</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>전세</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>60,000</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>팰루시드이강부동산공인중개사사무소</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>O매물답사가능O전세대출가능,냉장고,냉동,김냉,인덕션등</t>
-        </is>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>60000</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>전세</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>42489874</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>매교역팰루시드</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>101동</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>112.60</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>84.14</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>전세</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>55,000</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>팰루시드이강부동산공인중개사사무소</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>O조건맞춰찾아드립니다O이강에서집봐요,통근버스가까운동</t>
-        </is>
-      </c>
-      <c r="Y41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>55000</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>전세</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>42441234</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>매교역팰루시드</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>110동</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>112.60</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>84.14</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>전세</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>60,000</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>팰루시드이강부동산공인중개사사무소</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>O조건맞춰드립니다O커뮤니티코앞,동간격넓은동,입주일협의가능</t>
-        </is>
-      </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>60000</v>
-      </c>
-      <c r="AA42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5243,7 +4918,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>43126870</t>
+          <t>43165287</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -5253,27 +4928,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>111동</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>129.28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>101.73</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -5289,7 +4964,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>116,830</t>
+          <t>119,720</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -5304,7 +4979,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -5313,13 +4988,13 @@
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
@@ -5328,11 +5003,11 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>O이강은조건맞춰드립니다O뻥뷰,중도금대출승계가능</t>
+          <t>O정원뷰O2층커뮤니티동귀한대형평형시스템에어컨6대무상</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>116830</v>
+        <v>119720</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -5354,7 +5029,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43070705</t>
+          <t>43165270</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5415,7 +5090,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -5461,7 +5136,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>43070693</t>
+          <t>43165233</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5471,27 +5146,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>110동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>129.28</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>101.73</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -5507,7 +5182,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>119,372</t>
+          <t>116,830</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -5522,7 +5197,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -5533,12 +5208,12 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>O</t>
@@ -5546,11 +5221,11 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>O피500O로얄동,에어컨6,붙박이장,따뜻한단지조경뷰</t>
+          <t>O이강은조건맞춰드립니다O뻥뷰,중도금대출승계가능</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>119372</v>
+        <v>116830</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -5572,7 +5247,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>43070686</t>
+          <t>43164394</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5582,27 +5257,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>111동</t>
+          <t>109동</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>129.28</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>101.73</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -5618,7 +5293,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>119,720</t>
+          <t>115,272</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -5633,7 +5308,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -5649,19 +5324,19 @@
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>O정원뷰O2층커뮤니티동귀한대형평형시스템에어컨6대무상</t>
+          <t>O정상거래는이강O당일확인,에어컨4,붙박이장,인덕션</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>119720</v>
+        <v>115272</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -5683,7 +5358,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>42954753</t>
+          <t>43070693</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5693,27 +5368,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>129동</t>
+          <t>110동</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>84.42</t>
+          <t>129.28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>101.73</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -5729,7 +5404,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>89,000</t>
+          <t>119,372</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -5744,7 +5419,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -5761,14 +5436,18 @@
           <t>O</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>O조합원O필요금액확인요망,중문,초역세권동</t>
+          <t>O피500O로얄동,에어컨6,붙박이장,따뜻한단지조경뷰</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>89000</v>
+        <v>119372</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -5790,7 +5469,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>42952568</t>
+          <t>42954753</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -5800,12 +5479,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>105동</t>
+          <t>129동</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>84.42</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5820,7 +5499,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>고</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -5836,7 +5515,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>89,000</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -5871,11 +5550,11 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>O조합원매물설명必O손님분들전화환영합니다</t>
+          <t>O조합원O필요금액확인요망,중문,초역세권동</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>92000</v>
+        <v>89000</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -5897,7 +5576,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>42952544</t>
+          <t>42952568</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5907,27 +5586,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>109동</t>
+          <t>105동</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>고</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -5943,7 +5622,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>115,272</t>
+          <t>92,000</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -5967,11 +5646,7 @@
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
@@ -5982,11 +5657,11 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>O정상거래는이강O당일확인,에어컨4,붙박이장,인덕션</t>
+          <t>O조합원매물설명必O손님분들전화환영합니다</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>115272</v>
+        <v>92000</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -6117,7 +5792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA27"/>
+  <dimension ref="A1:AA24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6270,7 +5945,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>43160257</t>
+          <t>43166549</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -6280,27 +5955,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>122동</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>101.34</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>71.89</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -6321,7 +5996,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -6331,7 +6006,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -6340,14 +6015,18 @@
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>O</t>
@@ -6355,14 +6034,14 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>O채광좋은층O당일확인,중문,현관고급화</t>
+          <t>O대출가능,전입가능O2면창채광좋은집,에어컨4대</t>
         </is>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -6381,7 +6060,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43125582</t>
+          <t>43166533</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -6391,27 +6070,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>125동</t>
+          <t>120동</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>101.02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -6432,7 +6111,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -6442,7 +6121,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -6451,33 +6130,21 @@
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>O4년거주가능O대출가능,뻥뷰,에어컨4,인덕션등</t>
+          <t>O가격협의가능O이강에서집봐요,조건맞춰드립니다</t>
         </is>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>50000</v>
+        <v>45000</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -6496,7 +6163,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>43125573</t>
+          <t>43199433</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6506,27 +6173,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>122동</t>
+          <t>126동</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>101.34</t>
+          <t>84.42</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>71.89</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>고</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -6557,7 +6224,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -6577,15 +6244,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>O대출가능,전입가능O2면창채광좋은집,에어컨4대</t>
+          <t>O대출가능O융자없음.가전원옵션풀,시스템에어컨풀</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -6611,7 +6278,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>43125226</t>
+          <t>43164195</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6621,27 +6288,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>117동</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -6662,7 +6329,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -6672,7 +6339,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -6681,33 +6348,29 @@
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O채광좋은남동향,시에4,입주협의</t>
+          <t>O매물답사가능O전세대출가능,냉장고,냉동,김냉,인덕션등</t>
         </is>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>45000</v>
+        <v>60000</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -6726,7 +6389,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>43124673</t>
+          <t>43164078</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -6736,27 +6399,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>111동</t>
+          <t>103동</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>129.28</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>101.73</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -6777,7 +6440,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>70,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -6787,7 +6450,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -6796,29 +6459,25 @@
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>O전세는이강O귀한101타입,채광굿,입주일협의가능</t>
+          <t>O조건맞춰드립니다O초등학교인접인기동,시스템에어컨풀</t>
         </is>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>70000</v>
+        <v>50000</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -6837,7 +6496,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>43124662</t>
+          <t>43160257</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -6847,27 +6506,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>111동</t>
+          <t>104동</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -6888,7 +6547,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -6907,33 +6566,29 @@
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>O전세대출가능O융자없음,인덕션,시스템에어컨4,입주협의</t>
+          <t>O채광좋은층O당일확인,중문,현관고급화</t>
         </is>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>60000</v>
+        <v>45000</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -6952,7 +6607,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>43070764</t>
+          <t>43125226</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -6962,27 +6617,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>119동</t>
+          <t>104동</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -7003,7 +6658,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -7013,7 +6668,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -7022,8 +6677,16 @@
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
@@ -7033,14 +6696,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>O애완동물O,가격협의가O와이드주방,채광좋아요,조용하고따뜻한동</t>
+          <t>O조건맞춰드립니다O채광좋은남동향,시에4,입주협의</t>
         </is>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>55000</v>
+        <v>45000</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -7059,7 +6722,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>43028211</t>
+          <t>43124673</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7069,27 +6732,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>111동</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>129.28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>101.73</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -7110,7 +6773,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>53,000</t>
+          <t>70,000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -7120,7 +6783,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -7144,14 +6807,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>O채광좋은층O현금전세,밝고환한집,입주일협의</t>
+          <t>O전세는이강O귀한101타입,채광굿,입주일협의가능</t>
         </is>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>53000</v>
+        <v>70000</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -7170,7 +6833,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>43060055</t>
+          <t>43124662</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -7180,7 +6843,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>119동</t>
+          <t>111동</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -7200,7 +6863,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -7221,7 +6884,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>53,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -7231,7 +6894,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -7240,25 +6903,33 @@
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O현금전세,따뜻한단지내뷰,융무</t>
+          <t>O전세대출가능O융자없음,인덕션,시스템에어컨4,입주협의</t>
         </is>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>53000</v>
+        <v>60000</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -7277,7 +6948,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>43026195</t>
+          <t>43070764</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -7287,27 +6958,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>120동</t>
+          <t>119동</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>101.02</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -7328,7 +6999,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -7338,7 +7009,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -7351,17 +7022,21 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>O가격협의가능O이강에서집봐요,조건맞춰드립니다</t>
+          <t>O애완동물O,가격협의가O와이드주방,채광좋아요,조용하고따뜻한동</t>
         </is>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>45000</v>
+        <v>55000</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -7380,7 +7055,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>43026187</t>
+          <t>43060055</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -7390,27 +7065,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>131동</t>
+          <t>119동</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>74.16</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -7431,7 +7106,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>53,000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -7450,29 +7125,25 @@
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>O이.강O시에3,냉장고,냉동고,김치냉장고,워시타워,인덕션</t>
+          <t>O조건맞춰드립니다O현금전세,따뜻한단지내뷰,융무</t>
         </is>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>45000</v>
+        <v>53000</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -7491,7 +7162,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>43060057</t>
+          <t>43026187</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -7501,22 +7172,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>126동</t>
+          <t>131동</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>84.42</t>
+          <t>74.16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -7542,7 +7213,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -7567,11 +7238,7 @@
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
           <t>O</t>
@@ -7580,14 +7247,14 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
-          <t>O대출가능O융자없음.가전원옵션풀,시스템에어컨풀</t>
+          <t>O이.강O시에3,냉장고,냉동고,김치냉장고,워시타워,인덕션</t>
         </is>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>50000</v>
+        <v>45000</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -7606,7 +7273,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>42952893</t>
+          <t>42952675</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -7616,7 +7283,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>103동</t>
+          <t>119동</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -7636,7 +7303,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>중</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -7657,7 +7324,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -7676,25 +7343,21 @@
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O초등학교인접인기동,시스템에어컨풀</t>
+          <t>O조건맞춰찾아드립니다O전월세매물많은집</t>
         </is>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>50000</v>
+        <v>55000</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -7713,7 +7376,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>42952675</t>
+          <t>42952439</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -7723,7 +7386,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>119동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -7743,7 +7406,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -7759,12 +7422,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>116,830</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>52,000</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -7783,21 +7446,29 @@
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>O조건맞춰찾아드립니다O전월세매물많은집</t>
+          <t>O뻥뷰O현금전세,거실넓어요,에어컨4</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>116830</v>
       </c>
       <c r="Z15" t="n">
-        <v>55000</v>
+        <v>52000</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -7816,7 +7487,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>42952439</t>
+          <t>42962670</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -7826,7 +7497,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>105동</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -7846,7 +7517,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -7862,12 +7533,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>116,830</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>52,000</t>
+          <t>53,000</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7886,11 +7557,7 @@
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -7901,14 +7568,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>O뻥뷰O현금전세,거실넓어요,에어컨4</t>
+          <t>O현금전세O이.강조용한단지내뷰,나무보여요</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>116830</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>52000</v>
+        <v>53000</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -7927,7 +7594,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>42962670</t>
+          <t>42918213</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -7937,7 +7604,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>105동</t>
+          <t>102동</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -7957,7 +7624,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -7978,7 +7645,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>53,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7988,7 +7655,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -7999,23 +7666,23 @@
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
-          <t>O현금전세O이.강조용한단지내뷰,나무보여요</t>
+          <t>O조건맞춰드립니다O대출X초등학교가까운인기동</t>
         </is>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>53000</v>
+        <v>55000</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -8034,7 +7701,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>42918213</t>
+          <t>42852176</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -8044,7 +7711,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>102동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -8064,7 +7731,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>고</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -8085,7 +7752,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -8095,7 +7762,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -8111,18 +7778,22 @@
           <t>O</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O대출X초등학교가까운인기동</t>
+          <t>O조건맞춰드립니다O전세대출가능,조합원옵션굿</t>
         </is>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>55000</v>
+        <v>60000</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -8141,7 +7812,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>42852176</t>
+          <t>42747074</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -8151,27 +7822,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>129동</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>고</t>
+          <t>저</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -8192,7 +7863,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>47,000</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8202,7 +7873,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -8212,7 +7883,11 @@
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>O</t>
@@ -8226,14 +7901,14 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O전세대출가능,조합원옵션굿</t>
+          <t>O전세대출가능O매교역가까운동.빠른입주,중문인테리어</t>
         </is>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>60000</v>
+        <v>47000</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -8252,7 +7927,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>42747074</t>
+          <t>42704440</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -8262,33 +7937,33 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>129동</t>
+          <t>114동</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>저</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -8303,7 +7978,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>47,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8313,7 +7988,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -8322,12 +7997,12 @@
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
           <t>O</t>
@@ -8337,14 +8012,14 @@
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
-          <t>O전세대출가능O입주일협의,깨끗하게입주가능해요</t>
+          <t>O조건맞춰드립니다O전세대출가능,반전세가능,시스템풀</t>
         </is>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>47000</v>
+        <v>60000</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -8363,7 +8038,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>42704440</t>
+          <t>42558979</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -8373,33 +8048,33 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>114동</t>
+          <t>128동</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>101.02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -8414,7 +8089,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -8424,7 +8099,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -8433,29 +8108,29 @@
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O전세대출가능,반전세가능,시스템풀</t>
+          <t>O71타입로얄동O채광굿,입주협의가능</t>
         </is>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>60000</v>
+        <v>55000</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -8474,7 +8149,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>42558979</t>
+          <t>42490328</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -8484,33 +8159,33 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>128동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>101.02</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -8525,7 +8200,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -8535,7 +8210,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -8544,29 +8219,33 @@
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
-          <t>O71타입로얄동O채광굿,입주협의가능</t>
+          <t>O늦은입주OKO시에4,실링팬,중문,입주청소,예쁜집</t>
         </is>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>55000</v>
+        <v>60000</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -8585,7 +8264,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>42490328</t>
+          <t>42490321</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -8595,7 +8274,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>109동</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -8615,7 +8294,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>고</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -8636,7 +8315,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>57,000</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -8655,17 +8334,17 @@
         </is>
       </c>
       <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr">
         <is>
           <t>O</t>
@@ -8674,14 +8353,14 @@
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
         <is>
-          <t>O늦은입주OKO시에4,실링팬,중문,입주청소,예쁜집</t>
+          <t>O전세대출가능O입주청소,줄눈,탄성코팅,냉장고3대,인덕션등</t>
         </is>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>60000</v>
+        <v>57000</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -8700,7 +8379,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>42490321</t>
+          <t>42441234</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -8710,7 +8389,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>109동</t>
+          <t>110동</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -8730,7 +8409,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>고</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -8751,7 +8430,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>57,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -8761,7 +8440,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -8776,350 +8455,21 @@
           <t>O</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr">
         <is>
-          <t>O전세대출가능O입주청소,줄눈,탄성코팅,냉장고3대,인덕션등</t>
+          <t>O조건맞춰드립니다O커뮤니티코앞,동간격넓은동,입주일협의가능</t>
         </is>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>57000</v>
+        <v>60000</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>전세</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>42490045</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>매교역팰루시드</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>117동</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>112.60</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>84.14</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>전세</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>60,000</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>팰루시드이강부동산공인중개사사무소</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>O매물답사가능O전세대출가능,냉장고,냉동,김냉,인덕션등</t>
-        </is>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>60000</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>전세</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>42489874</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>매교역팰루시드</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>101동</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>112.60</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>84.14</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>전세</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>55,000</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>팰루시드이강부동산공인중개사사무소</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>O조건맞춰찾아드립니다O이강에서집봐요,통근버스가까운동</t>
-        </is>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>55000</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>전세</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>42441234</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>매교역팰루시드</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>110동</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>112.60</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>84.14</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>전세</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>60,000</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>팰루시드이강부동산공인중개사사무소</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>O조건맞춰드립니다O커뮤니티코앞,동간격넓은동,입주일협의가능</t>
-        </is>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>60000</v>
-      </c>
-      <c r="AA27" t="n">
         <v>0</v>
       </c>
     </row>
